--- a/jogos_2025-03-12.xlsx
+++ b/jogos_2025-03-12.xlsx
@@ -901,16 +901,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Radnički Sr. Mitrovica</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -919,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X4" t="n">
         <v>2.25</v>
       </c>
-      <c r="M4" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" t="n">
+      <c r="Y4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI4" t="n">
         <v>1.5</v>
       </c>
-      <c r="S4" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['87']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['14']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45728.41666666666</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,19 +1030,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.63</v>
+        <v>11</v>
       </c>
       <c r="M5" t="n">
-        <v>3.18</v>
+        <v>4.75</v>
       </c>
       <c r="N5" t="n">
-        <v>5.52</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.75</v>
+        <v>1.91</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>2.37</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X5" t="n">
         <v>3.3</v>
       </c>
-      <c r="U5" t="n">
+      <c r="Y5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.29</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['90+3']</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45728.41666666666</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.47</v>
+        <v>2.26</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>7.5</v>
+        <v>3.23</v>
       </c>
       <c r="O6" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['15', '53']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>2.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['50', '53', '66', '84']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>4.75</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45728.41666666666</v>
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Radnički Sr. Mitrovica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,22 +1314,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.64</v>
+        <v>2.15</v>
       </c>
       <c r="M7" t="n">
-        <v>3.68</v>
+        <v>3.41</v>
       </c>
       <c r="N7" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
         <v>1.44</v>
@@ -1341,16 +1341,16 @@
         <v>3.1</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="X7" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="Y7" t="n">
         <v>2.2</v>
@@ -1359,16 +1359,16 @@
         <v>1.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.55</v>
+        <v>4.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['16', '36']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45728.41666666666</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1432,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1443,65 +1443,65 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45728.41666666666</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Sloven Ruma</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
         <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="N9" t="n">
-        <v>3.23</v>
+        <v>2.96</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="R9" t="n">
         <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W9" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="X9" t="n">
-        <v>3.25</v>
+        <v>2.52</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.94</v>
+        <v>2.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.35</v>
+        <v>4.65</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>['11', '61', '76']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['15', '53']</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AI9" t="n">
         <v>1.73</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45728.41666666666</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,22 +1675,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mladost Novi Sad</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45728.41666666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,16 +1804,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Mladost Novi Sad</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1830,65 +1830,65 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="M11" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="V11" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="W11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1.4</v>
       </c>
-      <c r="X11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AA11" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1900,13 +1900,13 @@
         <v>1.44</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45728.41666666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="M12" t="n">
-        <v>3.41</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="R12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="Z12" t="n">
         <v>1.44</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W12" t="n">
+      <c r="AA12" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['50', '53', '66', '84']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.4</v>
       </c>
-      <c r="X12" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['16', '36']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45728.41666666666</v>
@@ -2062,51 +2062,51 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sloven Ruma</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="N13" t="n">
-        <v>2.96</v>
+        <v>3.19</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
         <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
         <v>2.45</v>
@@ -2121,19 +2121,19 @@
         <v>1.07</v>
       </c>
       <c r="W13" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
-        <v>2.52</v>
+        <v>2.37</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="AB13" t="n">
         <v>1.12</v>
@@ -2146,25 +2146,25 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['11', '61', '76']</t>
+          <t>['87']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45728.41666666666</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.6</v>
+        <v>1.63</v>
       </c>
       <c r="M14" t="n">
-        <v>3.75</v>
+        <v>3.18</v>
       </c>
       <c r="N14" t="n">
-        <v>1.67</v>
+        <v>5.52</v>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
         <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="T14" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="V14" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="X14" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.15</v>
+        <v>4.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['23', '79']</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.16</v>
+        <v>1.63</v>
       </c>
       <c r="AI14" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45728.41666666666</v>
@@ -2320,16 +2320,16 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>2</v>
@@ -2338,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>11</v>
+        <v>4.6</v>
       </c>
       <c r="M15" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="O15" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['23', '79']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45728.41666666666</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
         <v>1</v>
       </c>
-      <c r="H18" t="n">
-        <v>2</v>
-      </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="N18" t="n">
-        <v>7.35</v>
+        <v>1.57</v>
       </c>
       <c r="O18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.56</v>
+        <v>1.83</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.45</v>
+        <v>1.91</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['8', '82']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['52', '90+5']</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45728.45833333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
-        <v>3.78</v>
+        <v>3.83</v>
       </c>
       <c r="N19" t="n">
-        <v>1.57</v>
+        <v>7.35</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.83</v>
+        <v>2.56</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['8', '82']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>['52', '90+5']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45728.45833333334</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.65</v>
+        <v>1.23</v>
       </c>
       <c r="M23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>10</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S23" t="n">
         <v>3.25</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.9</v>
-      </c>
       <c r="T23" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="U23" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="V23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['31', '42', '56', '83', '89']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
         <v>1.02</v>
       </c>
-      <c r="W23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>3.75</v>
       </c>
       <c r="AI23" t="n">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.89</v>
+        <v>6.5</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45728.58333333334</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,109 +3481,109 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI24" t="n">
         <v>2</v>
       </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="M24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>10</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['31', '42', '56', '83', '89']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['21']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>6.5</v>
+        <v>1.89</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45728.58333333334</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cape Town City</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,22 +3894,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.76</v>
+        <v>2.24</v>
       </c>
       <c r="M27" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="O27" t="n">
         <v>3.1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.5</v>
       </c>
       <c r="P27" t="n">
         <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
         <v>1.5</v>
@@ -3918,37 +3918,37 @@
         <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V27" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="X27" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA27" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3957,20 +3957,20 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '64']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.95</v>
+        <v>1.49</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45728.60416666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="M29" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R29" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="S29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>2.63</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>['90+4']</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45728.60416666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,25 +4255,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Messina</t>
+          <t>Cape Town City</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,52 +4281,52 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="O30" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P30" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R30" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S30" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="T30" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V30" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W30" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X30" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AB30" t="n">
         <v>1.17</v>
@@ -4339,25 +4339,25 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['49', '51', '57']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['29', '58', '61']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45728.60416666666</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,22 +4384,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="M31" t="n">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="N31" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="O31" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="R31" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="S31" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U31" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="V31" t="n">
         <v>1.11</v>
       </c>
       <c r="W31" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X31" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="Z31" t="n">
         <v>1.48</v>
       </c>
       <c r="AA31" t="n">
-        <v>5.75</v>
+        <v>4.33</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
+          <t>['17', '40']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['48']</t>
-        </is>
-      </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45728.60416666666</v>
@@ -4513,22 +4513,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4539,74 +4539,74 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.86</v>
+        <v>2.39</v>
       </c>
       <c r="M32" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="N32" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T32" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="V32" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="W32" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="X32" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC32" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['17', '40']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AH32" t="n">
         <v>1.53</v>
@@ -4615,7 +4615,7 @@
         <v>1.8</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45728.60416666666</v>
@@ -4642,19 +4642,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Messina</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.24</v>
+        <v>1.75</v>
       </c>
       <c r="M33" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="N33" t="n">
-        <v>3.26</v>
+        <v>5.3</v>
       </c>
       <c r="O33" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="P33" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S33" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="T33" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="U33" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W33" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="X33" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['49', '51', '57']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['29', '58', '61']</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ33" t="n">
         <v>2.75</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['20', '64']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45728.60416666666</v>
@@ -5029,48 +5029,48 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Sandhausen</t>
         </is>
       </c>
       <c r="G36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.71</v>
+        <v>2.05</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="N36" t="n">
-        <v>2.5</v>
+        <v>3.26</v>
       </c>
       <c r="O36" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="P36" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="R36" t="n">
         <v>1.33</v>
@@ -5079,10 +5079,10 @@
         <v>3</v>
       </c>
       <c r="T36" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="V36" t="n">
         <v>1.05</v>
@@ -5091,7 +5091,7 @@
         <v>1.25</v>
       </c>
       <c r="X36" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="Y36" t="n">
         <v>1.73</v>
@@ -5100,38 +5100,38 @@
         <v>2</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AB36" t="n">
         <v>1.38</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>['14', '32', '38']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43', '61']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AI36" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45728.625</v>
@@ -5158,25 +5158,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Borussia Dortmund II</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U37" t="n">
         <v>1.44</v>
       </c>
-      <c r="M37" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="N37" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>5</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.68</v>
-      </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W37" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="X37" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.42</v>
+        <v>1.89</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.7</v>
+        <v>1.93</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.66</v>
+        <v>1.33</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '15', '35', '86']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.95</v>
+        <v>2.35</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45728.625</v>
@@ -5287,25 +5287,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sandhausen</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,22 +5313,22 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.05</v>
+        <v>2.71</v>
       </c>
       <c r="M38" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>3.26</v>
+        <v>2.5</v>
       </c>
       <c r="O38" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="P38" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="R38" t="n">
         <v>1.33</v>
@@ -5337,10 +5337,10 @@
         <v>3</v>
       </c>
       <c r="T38" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U38" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="V38" t="n">
         <v>1.05</v>
@@ -5349,7 +5349,7 @@
         <v>1.25</v>
       </c>
       <c r="X38" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Y38" t="n">
         <v>1.73</v>
@@ -5358,38 +5358,38 @@
         <v>2</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AB38" t="n">
         <v>1.38</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['14', '32', '38']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['43', '61']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45728.625</v>
@@ -5416,25 +5416,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,28 +5442,28 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="M39" t="n">
-        <v>3.2</v>
+        <v>3.51</v>
       </c>
       <c r="N39" t="n">
-        <v>3.91</v>
+        <v>3.22</v>
       </c>
       <c r="O39" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="P39" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S39" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="T39" t="n">
         <v>2.55</v>
@@ -5478,47 +5478,47 @@
         <v>1.28</v>
       </c>
       <c r="X39" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AD39" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['3', '15', '35', '86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45728.625</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Borussia Dortmund II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="M40" t="n">
-        <v>3.51</v>
+        <v>5.03</v>
       </c>
       <c r="N40" t="n">
-        <v>3.22</v>
+        <v>5.89</v>
       </c>
       <c r="O40" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>5</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X40" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z40" t="n">
         <v>2.7</v>
       </c>
-      <c r="P40" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X40" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AA40" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,16 +5638,16 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.65</v>
+        <v>2.6</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.78</v>
+        <v>1.42</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.2</v>
+        <v>2.95</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45728.625</v>
@@ -5803,109 +5803,109 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
         <v>2</v>
       </c>
-      <c r="H42" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.02</v>
+        <v>3.48</v>
       </c>
       <c r="M42" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="N42" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="O42" t="n">
-        <v>4.51</v>
+        <v>4.28</v>
       </c>
       <c r="P42" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="R42" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="S42" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="T42" t="n">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="U42" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V42" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W42" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="X42" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="Z42" t="n">
         <v>1.39</v>
       </c>
       <c r="AA42" t="n">
-        <v>5.5</v>
+        <v>5.81</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['70', '89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>['30', '45+2', '74']</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AI42" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45728.6875</v>
@@ -5932,19 +5932,19 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.7</v>
+        <v>3.02</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>2.77</v>
       </c>
       <c r="N43" t="n">
-        <v>5.3</v>
+        <v>2.65</v>
       </c>
       <c r="O43" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S43" t="n">
         <v>2.28</v>
       </c>
-      <c r="P43" t="n">
+      <c r="T43" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC43" t="n">
         <v>2.17</v>
       </c>
-      <c r="Q43" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T43" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X43" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AD43" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['70', '89']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.11</v>
+        <v>1.52</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.06</v>
+        <v>1.27</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AJ43" t="n">
-        <v>3.12</v>
+        <v>1.89</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45728.6875</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,109 +6061,109 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N44" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X44" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>['42', '59']</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ44" t="n">
         <v>3</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>2</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="M44" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="N44" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="O44" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="P44" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T44" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="X44" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>['30', '45+2', '74']</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1.88</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45728.6875</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,22 +6190,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -6219,62 +6219,62 @@
         <v>1.7</v>
       </c>
       <c r="M45" t="n">
-        <v>3.41</v>
+        <v>3.45</v>
       </c>
       <c r="N45" t="n">
         <v>5.3</v>
       </c>
       <c r="O45" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.75</v>
+        <v>5.81</v>
       </c>
       <c r="R45" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="S45" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T45" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="U45" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="V45" t="n">
         <v>1.02</v>
       </c>
       <c r="W45" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="X45" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AA45" t="n">
-        <v>4.2</v>
+        <v>3.97</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AD45" t="n">
         <v>1.67</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>['42', '59']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -6283,16 +6283,16 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AJ45" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45728.6875</v>
@@ -6319,54 +6319,54 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
         <v>2</v>
       </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
       <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
         <v>1</v>
       </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.28</v>
+        <v>1.9</v>
       </c>
       <c r="M46" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>9.4</v>
+        <v>4</v>
       </c>
       <c r="O46" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="P46" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q46" t="n">
-        <v>9.5</v>
+        <v>4.33</v>
       </c>
       <c r="R46" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S46" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T46" t="n">
         <v>2.63</v>
@@ -6375,13 +6375,13 @@
         <v>1.44</v>
       </c>
       <c r="V46" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W46" t="n">
         <v>1.25</v>
       </c>
       <c r="X46" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="Y46" t="n">
         <v>1.77</v>
@@ -6390,38 +6390,38 @@
         <v>1.98</v>
       </c>
       <c r="AA46" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AB46" t="n">
         <v>1.38</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['3', '85']</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['44', '49']</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AH46" t="n">
-        <v>3.55</v>
+        <v>1.83</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AJ46" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45728.69791666666</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,20 +6448,20 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
         <v>2</v>
       </c>
-      <c r="H47" t="n">
-        <v>1</v>
-      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="M47" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="N47" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="O47" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="P47" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="R47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U47" t="n">
         <v>1.44</v>
       </c>
-      <c r="S47" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T47" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.33</v>
-      </c>
       <c r="V47" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W47" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="X47" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.8</v>
+        <v>2.66</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AC47" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD47" t="n">
         <v>2</v>
       </c>
-      <c r="AD47" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['73', '76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['52', '63']</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AJ47" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45728.69791666666</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,19 +6577,19 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Taranto</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -6599,87 +6599,87 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73', '76']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45728.69791666666</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,25 +6706,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
         <v>1</v>
       </c>
-      <c r="H49" t="n">
-        <v>1</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.07</v>
+        <v>1.28</v>
       </c>
       <c r="M49" t="n">
-        <v>3.35</v>
+        <v>5.4</v>
       </c>
       <c r="N49" t="n">
-        <v>3.47</v>
+        <v>9.4</v>
       </c>
       <c r="O49" t="n">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="P49" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.4</v>
+        <v>9.5</v>
       </c>
       <c r="R49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U49" t="n">
         <v>1.44</v>
       </c>
-      <c r="S49" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.33</v>
-      </c>
       <c r="V49" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W49" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="X49" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AA49" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['3', '85']</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.27</v>
+        <v>1.05</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.72</v>
+        <v>3.55</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.83</v>
+        <v>1.2</v>
       </c>
       <c r="AJ49" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45728.69791666666</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,48 +6835,48 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
         <v>1</v>
       </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="M50" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="N50" t="n">
-        <v>3.07</v>
+        <v>3.47</v>
       </c>
       <c r="O50" t="n">
         <v>3.1</v>
       </c>
       <c r="P50" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R50" t="n">
         <v>1.44</v>
@@ -6885,59 +6885,59 @@
         <v>2.63</v>
       </c>
       <c r="T50" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U50" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V50" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W50" t="n">
         <v>1.36</v>
       </c>
       <c r="X50" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AA50" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AB50" t="n">
         <v>1.25</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['27']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45728.69791666666</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,19 +7093,19 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Taranto</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -7115,65 +7115,65 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7182,20 +7182,20 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>['52', '63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45728.69791666666</v>
@@ -7351,25 +7351,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G54" t="n">
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="M54" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="N54" t="n">
-        <v>4</v>
+        <v>3.07</v>
       </c>
       <c r="O54" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="P54" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X54" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ54" t="n">
         <v>2.25</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S54" t="n">
-        <v>3</v>
-      </c>
-      <c r="T54" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X54" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>['89']</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>['44', '49']</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>2.6</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45728.69791666666</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,83 +7506,83 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="M55" t="n">
-        <v>3.53</v>
+        <v>3.29</v>
       </c>
       <c r="N55" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="O55" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P55" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R55" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S55" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="T55" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="U55" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="V55" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="W55" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="X55" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.62</v>
+        <v>3.95</v>
       </c>
       <c r="AB55" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH55" t="n">
         <v>1.48</v>
       </c>
-      <c r="AC55" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>['1']</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AI55" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45728.70833333334</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,83 +7764,83 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="M57" t="n">
-        <v>3.29</v>
+        <v>3.53</v>
       </c>
       <c r="N57" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="O57" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P57" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R57" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S57" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="T57" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="U57" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="V57" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W57" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="X57" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AA57" t="n">
-        <v>3.95</v>
+        <v>2.62</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AC57" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>['1']</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG57" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ57" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>['19']</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG57" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45728.70833333334</v>
@@ -7996,109 +7996,109 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M59" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N59" t="n">
         <v>2</v>
       </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M59" t="n">
-        <v>4</v>
-      </c>
-      <c r="N59" t="n">
-        <v>5.6</v>
-      </c>
       <c r="O59" t="n">
-        <v>2.38</v>
+        <v>6</v>
       </c>
       <c r="P59" t="n">
         <v>2.2</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.33</v>
+        <v>2.05</v>
       </c>
       <c r="R59" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S59" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X59" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>['87']</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG59" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ59" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S59" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T59" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U59" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W59" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X59" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>['10', '13', '75']</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG59" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>2.88</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45728.72916666666</v>
@@ -8125,22 +8125,22 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -8151,83 +8151,83 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="M60" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="N60" t="n">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="O60" t="n">
-        <v>6</v>
+        <v>2.38</v>
       </c>
       <c r="P60" t="n">
         <v>2.2</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.05</v>
+        <v>4.33</v>
       </c>
       <c r="R60" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S60" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="T60" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="U60" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="V60" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W60" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X60" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>['10', '13', '75']</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG60" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI60" t="n">
         <v>1.5</v>
       </c>
-      <c r="X60" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>['87']</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG60" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AJ60" t="n">
-        <v>1.36</v>
+        <v>2.88</v>
       </c>
       <c r="AK60" s="3" t="n">
         <v>45728.72916666666</v>
